--- a/apps/student/public/templates/teachers-import.xlsx
+++ b/apps/student/public/templates/teachers-import.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教师名单" sheetId="1" r:id="Rbfe6ef5433b44f73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R1bc7ab178899402e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教师名单" sheetId="1" r:id="R5071c017e83d4d79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="Rb6e4b17fecb247aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,7 +17,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -45,8 +45,20 @@
       <x:color rgb="FF1D4ED8"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1E3A8A"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1E3A8A"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -63,6 +75,16 @@
         <x:fgColor rgb="FFEFF6FF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAFE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAFE"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border>
@@ -76,7 +98,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -88,6 +110,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -290,37 +318,43 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="32" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="32" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="32" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="19" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="19" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="19" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="19" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="19" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="19" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="19" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="13" t="str">
         <x:v>登录手机号</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="str">
+      <x:c r="B1" s="13" t="str">
         <x:v>教师姓名</x:v>
       </x:c>
-      <x:c r="C1" s="4" t="str">
-        <x:v>教师工号</x:v>
-      </x:c>
-      <x:c r="D1" s="4" t="str">
+      <x:c r="C1" s="13" t="str">
         <x:v>任教学科</x:v>
       </x:c>
-      <x:c r="E1" s="4" t="str">
-        <x:v>教师角色</x:v>
-      </x:c>
-      <x:c r="F1" s="4" t="str">
+      <x:c r="D1" s="13" t="str">
         <x:v>任教班级</x:v>
       </x:c>
-      <x:c r="G1" s="4" t="str">
+      <x:c r="E1" s="13" t="str">
         <x:v>班主任班级</x:v>
       </x:c>
+      <x:c r="F1" s="13" t="str">
+        <x:v>年级组长年级</x:v>
+      </x:c>
+      <x:c r="G1" s="13" t="str">
+        <x:v>教研组长学科</x:v>
+      </x:c>
+      <x:c r="H1" s="14" t="str">
+        <x:v>专业技术职称</x:v>
+      </x:c>
+      <x:c r="I1" s="12"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="2"/>
@@ -1236,8 +1270,8 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="115" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="21" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="88" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
@@ -1258,7 +1292,7 @@
         <x:v>登录手机号</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>必填，11位手机号；用作登录名，不得与已有账号重复。</x:v>
+        <x:v>必填；填写有效的11位手机号，并按文本格式保存。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="36" customHeight="1">
@@ -1266,88 +1300,108 @@
         <x:v>教师姓名</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
-        <x:v>必填，填写教师真实姓名。</x:v>
+        <x:v>必填；填写教师真实姓名。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="36" customHeight="1">
       <x:c r="A7" s="1" t="str">
-        <x:v>教师工号</x:v>
+        <x:v>任教学科</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
-        <x:v>选填，按文本填写，保留前导零。</x:v>
+        <x:v>必填；可填写多门学科，用顿号分隔。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="36" customHeight="1">
       <x:c r="A8" s="1" t="str">
-        <x:v>任教学科</x:v>
+        <x:v>任教班级</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>必填，多科用顿号分隔，如：英语、道德与法治。</x:v>
+        <x:v>建议填写；多个班级用顿号分隔，留空表示未分配。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="36" customHeight="1">
       <x:c r="A9" s="1" t="str">
-        <x:v>教师角色</x:v>
+        <x:v>班主任班级</x:v>
       </x:c>
       <x:c r="B9" s="6" t="str">
-        <x:v>必填：教师、班主任、学校管理员。</x:v>
+        <x:v>选填；填写后形成班主任任职，每班只能有一位班主任。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="36" customHeight="1">
       <x:c r="A10" s="1" t="str">
-        <x:v>任教班级</x:v>
+        <x:v>年级组长年级</x:v>
       </x:c>
       <x:c r="B10" s="6" t="str">
-        <x:v>建议填写；多个班级用顿号分隔，留空表示未分配。</x:v>
+        <x:v>选填；填写1至9的数字，多个年级用顿号分隔。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="36" customHeight="1">
       <x:c r="A11" s="1" t="str">
-        <x:v>班主任班级</x:v>
+        <x:v>教研组长学科</x:v>
       </x:c>
       <x:c r="B11" s="6" t="str">
-        <x:v>仅班主任角色填写；每班只能有一位班主任。</x:v>
+        <x:v>选填；使用可选学科名称，多个学科用顿号分隔。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="36" customHeight="1">
       <x:c r="A12" s="1" t="str">
-        <x:v>可选学科</x:v>
+        <x:v>专业技术职称</x:v>
       </x:c>
       <x:c r="B12" s="6" t="str">
-        <x:v>语文、数学、英语、物理、化学、生物、道德与法治、历史、地理、科学、体育、音乐、美术、信息科技、劳动。</x:v>
+        <x:v>选填；如一级教师、高级教师，与校内任职分开。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="36" customHeight="1">
       <x:c r="A13" s="1" t="str">
-        <x:v>填写班级</x:v>
+        <x:v>可选学科</x:v>
       </x:c>
       <x:c r="B13" s="6" t="str">
-        <x:v>班级名称须与平台一致，请在导入页面查看现有班级。</x:v>
+        <x:v>语文、数学、英语、物理、化学、生物、道德与法治、历史、地理、科学、体育、音乐、美术、信息科技、劳动。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="36" customHeight="1">
       <x:c r="A14" s="1" t="str">
-        <x:v>填写方法</x:v>
+        <x:v>填写班级</x:v>
       </x:c>
       <x:c r="B14" s="6" t="str">
-        <x:v>在教师名单第2行开始填；不改表头，不填公式；手机号和工号使用文本格式。</x:v>
+        <x:v>班级名称须与平台一致，请在导入页面查看现有班级。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="36" customHeight="1">
       <x:c r="A15" s="1" t="str">
-        <x:v>示例（不导入）</x:v>
+        <x:v>填写方法</x:v>
       </x:c>
       <x:c r="B15" s="6" t="str">
-        <x:v>13900000002 | 张老师 | T002 | 英语、道德与法治 | 教师 | 七年级(2)班、七年级(4)班 | 留空</x:v>
+        <x:v>在教师名单第2行开始填；不改表头，不填公式；手机号使用文本格式。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="36" customHeight="1">
       <x:c r="A16" s="1" t="str">
+        <x:v>系统权限</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>本模板不导入系统权限。任职和职称不会自动授权，需在教师列表单独维护。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>示例（不导入）</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>13900000002 | 张老师 | 英语 | 七年级(2)班 | 留空 | 7 | 英语 | 一级教师</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
         <x:v>校验与导入</x:v>
       </x:c>
-      <x:c r="B16" s="6" t="str">
+      <x:c r="B18" t="str">
         <x:v>上传后查看逐行校验结果，全部通过后点击确认导入。</x:v>
       </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/apps/student/public/templates/teachers-import.xlsx
+++ b/apps/student/public/templates/teachers-import.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教师名单" sheetId="1" r:id="R5071c017e83d4d79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="Rb6e4b17fecb247aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教师名单" sheetId="1" r:id="R8b478cddd6f84fd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R43523e19f8894a2b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -351,9 +351,7 @@
       <x:c r="G1" s="13" t="str">
         <x:v>教研组长学科</x:v>
       </x:c>
-      <x:c r="H1" s="14" t="str">
-        <x:v>专业技术职称</x:v>
-      </x:c>
+      <x:c r="H1"/>
       <x:c r="I1" s="12"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
@@ -1345,59 +1343,55 @@
     </x:row>
     <x:row r="12" ht="36" customHeight="1">
       <x:c r="A12" s="1" t="str">
-        <x:v>专业技术职称</x:v>
+        <x:v>可选学科</x:v>
       </x:c>
       <x:c r="B12" s="6" t="str">
-        <x:v>选填；如一级教师、高级教师，与校内任职分开。</x:v>
+        <x:v>语文、数学、英语、物理、化学、生物、道德与法治、历史、地理、科学、体育、音乐、美术、信息科技、劳动。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="36" customHeight="1">
       <x:c r="A13" s="1" t="str">
-        <x:v>可选学科</x:v>
+        <x:v>填写班级</x:v>
       </x:c>
       <x:c r="B13" s="6" t="str">
-        <x:v>语文、数学、英语、物理、化学、生物、道德与法治、历史、地理、科学、体育、音乐、美术、信息科技、劳动。</x:v>
+        <x:v>班级名称须与平台一致，请在导入页面查看现有班级。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="36" customHeight="1">
       <x:c r="A14" s="1" t="str">
-        <x:v>填写班级</x:v>
+        <x:v>填写方法</x:v>
       </x:c>
       <x:c r="B14" s="6" t="str">
-        <x:v>班级名称须与平台一致，请在导入页面查看现有班级。</x:v>
+        <x:v>在教师名单第2行开始填；不改表头，不填公式；手机号使用文本格式。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="36" customHeight="1">
       <x:c r="A15" s="1" t="str">
-        <x:v>填写方法</x:v>
+        <x:v>系统权限</x:v>
       </x:c>
       <x:c r="B15" s="6" t="str">
-        <x:v>在教师名单第2行开始填；不改表头，不填公式；手机号使用文本格式。</x:v>
+        <x:v>本模板不导入系统权限。任职不会自动授权，需在教师列表单独维护。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="36" customHeight="1">
       <x:c r="A16" s="1" t="str">
-        <x:v>系统权限</x:v>
+        <x:v>示例（不导入）</x:v>
       </x:c>
       <x:c r="B16" s="6" t="str">
-        <x:v>本模板不导入系统权限。任职和职称不会自动授权，需在教师列表单独维护。</x:v>
+        <x:v>13900000002 | 张老师 | 英语 | 七年级(2)班 | 留空 | 7 | 英语</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>示例（不导入）</x:v>
+        <x:v>校验与导入</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>13900000002 | 张老师 | 英语 | 七年级(2)班 | 留空 | 7 | 英语 | 一级教师</x:v>
+        <x:v>上传后查看逐行校验结果，全部通过后点击确认导入。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" t="str">
-        <x:v>校验与导入</x:v>
-      </x:c>
-      <x:c r="B18" t="str">
-        <x:v>上传后查看逐行校验结果，全部通过后点击确认导入。</x:v>
-      </x:c>
+      <x:c r="A18"/>
+      <x:c r="B18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
